--- a/config.xlsx
+++ b/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Elias\Documents\Luis_automatizacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57DB5721-C5F1-460E-A0AB-8C9D5830DDED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2764F11D-EFB7-4EEF-A572-7C3057415C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -69,7 +69,7 @@
     <t>DEICY TATIANA ROMERO GUIO</t>
   </si>
   <si>
-    <t>2026-ER-0430250</t>
+    <t>2026-ER-0436572</t>
   </si>
 </sst>
 </file>
